--- a/examples/04-images-charts.xlsx
+++ b/examples/04-images-charts.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Pie chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -174,12 +175,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Data'!$A$2:$A$5</f>
+              <f>'Data'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$2:$B$5</f>
+              <f>'Data'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -198,12 +199,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Data'!$A$2:$A$5</f>
+              <f>'Data'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$C$2:$C$5</f>
+              <f>'Data'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -229,6 +230,21 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>k UAH</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -255,15 +271,16 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenue trend</a:t>
+              <a:t>Stacked (horizontal)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -277,28 +294,46 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Data'!$A$2:$A$5</f>
+              <f>'Data'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$2:$B$5</f>
+              <f>'Data'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Data'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$C$2:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -343,6 +378,495 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Revenue trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Data'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Costs (area)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <areaChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Data'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$C$2:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </areaChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Visitors vs revenue</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Months</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="diamond"/>
+            <size val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'Data'!$D$2:$D$7</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Data'!$B$2:$B$7</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Visitors</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Revenue</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Visitors and conversion</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Data'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$2:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Data'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Data'!$E$2:$E$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="200"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="200"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Conversion</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <crosses val="max"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Costs share</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <doughnutChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Data'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$C$2:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+        <holeSize val="10"/>
+      </doughnutChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Revenue share</a:t>
             </a:r>
           </a:p>
@@ -367,12 +891,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Data'!$A$2:$A$5</f>
+              <f>'Data'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$2:$B$5</f>
+              <f>'Data'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -398,7 +922,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -420,9 +944,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>15</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -442,7 +966,95 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
@@ -450,11 +1062,36 @@
     <ext cx="1143000" cy="381000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>95250</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="571500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -469,6 +1106,33 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="0" y="0"/>
@@ -779,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +1462,16 @@
           <t>Costs</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Visitors</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -811,6 +1485,12 @@
       <c r="C2" t="n">
         <v>30</v>
       </c>
+      <c r="D2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.021</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -824,6 +1504,12 @@
       <c r="C3" t="n">
         <v>31</v>
       </c>
+      <c r="D3" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.024</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -837,6 +1523,12 @@
       <c r="C4" t="n">
         <v>35</v>
       </c>
+      <c r="D4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.022</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +1542,72 @@
       <c r="C5" t="n">
         <v>33</v>
       </c>
+      <c r="D5" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>58</v>
+      </c>
+      <c r="C6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.027</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>63</v>
+      </c>
+      <c r="C7" t="n">
+        <v>40</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>A chart on another sheet, built from the Data sheet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/04-images-charts.xlsx
+++ b/examples/04-images-charts.xlsx
@@ -140,6 +140,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -261,6 +262,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -368,6 +370,7 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -457,6 +460,7 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -537,6 +541,7 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <style val="13"/>
   <chart>
     <title>
@@ -658,6 +663,7 @@
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>

--- a/examples/04-images-charts.xlsx
+++ b/examples/04-images-charts.xlsx
@@ -141,6 +141,14 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <chart>
     <title>
       <tx>
@@ -257,6 +265,13 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <extLst>
+    <ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+      <c16r3:dataDisplayOptions16>
+        <c16r3:dispNaAsBlank val="1"/>
+      </c16r3:dataDisplayOptions16>
+    </ext>
+  </extLst>
 </chartSpace>
 </file>
 
@@ -916,6 +931,46 @@
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
